--- a/R Markdown/resultados/tabelas_alocacao_subprefeituras.xlsx
+++ b/R Markdown/resultados/tabelas_alocacao_subprefeituras.xlsx
@@ -1833,7 +1833,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1849,30 +1849,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>populacao</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>idrgp_alvo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>idrgp_real</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>status_estatistico</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>idrgp_alvo_pct</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>idrgp_real_pct</t>
         </is>
@@ -1890,23 +1895,26 @@
         </is>
       </c>
       <c r="C2">
+        <v>412804</v>
+      </c>
+      <c r="D2">
         <v>1688434491</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0.05427611013661751</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.02953342009533873</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G2">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H2">
         <v>5.427611013661751</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>2.953342009533873</v>
       </c>
     </row>
@@ -1922,23 +1930,26 @@
         </is>
       </c>
       <c r="C3">
+        <v>570809</v>
+      </c>
+      <c r="D3">
         <v>3036975936.59</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0.0768001000600067</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.05312156712791723</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G3">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H3">
         <v>7.68001000600067</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>5.312156712791723</v>
       </c>
     </row>
@@ -1954,23 +1965,26 @@
         </is>
       </c>
       <c r="C4">
+        <v>354316</v>
+      </c>
+      <c r="D4">
         <v>2415839399.78</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0.01518693116727706</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.0422568955188287</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>1.518693116727706</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>4.22568955188287</v>
       </c>
     </row>
@@ -1986,23 +2000,26 @@
         </is>
       </c>
       <c r="C5">
+        <v>480878</v>
+      </c>
+      <c r="D5">
         <v>1586731737.63</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>0.02852737800077722</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.02775447625349036</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G5">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H5">
         <v>2.852737800077722</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>2.775447625349036</v>
       </c>
     </row>
@@ -2018,23 +2035,26 @@
         </is>
       </c>
       <c r="C6">
+        <v>338347</v>
+      </c>
+      <c r="D6">
         <v>1635541987.13</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>0.01196759457375883</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.02860824559492808</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>1.196759457375883</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>2.860824559492808</v>
       </c>
     </row>
@@ -2050,23 +2070,26 @@
         </is>
       </c>
       <c r="C7">
+        <v>214958</v>
+      </c>
+      <c r="D7">
         <v>1532982112.9</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>0.0146420577822676</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.0268143093381736</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>1.46420577822676</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>2.68143093381736</v>
       </c>
     </row>
@@ -2082,23 +2105,26 @@
         </is>
       </c>
       <c r="C8">
+        <v>276378</v>
+      </c>
+      <c r="D8">
         <v>1001849833.82</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>0.03106350078710079</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.01752395616908264</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G8">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H8">
         <v>3.106350078710079</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>1.752395616908264</v>
       </c>
     </row>
@@ -2114,23 +2140,26 @@
         </is>
       </c>
       <c r="C9">
+        <v>272332</v>
+      </c>
+      <c r="D9">
         <v>1665436605.22</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>0.00780842708567104</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0.02913115028524791</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.780842708567104</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>2.913115028524791</v>
       </c>
     </row>
@@ -2146,23 +2175,26 @@
         </is>
       </c>
       <c r="C10">
+        <v>266715</v>
+      </c>
+      <c r="D10">
         <v>1078636355.45</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>0.02854078087441063</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>0.01886707526138185</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G10">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H10">
         <v>2.854078087441063</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>1.886707526138185</v>
       </c>
     </row>
@@ -2178,23 +2210,26 @@
         </is>
       </c>
       <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
         <v>1362970185.21</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>0.03997675152969091</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.02384052876898294</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G11">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H11">
         <v>3.997675152969091</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>2.384052876898294</v>
       </c>
     </row>
@@ -2210,23 +2245,26 @@
         </is>
       </c>
       <c r="C12">
+        <v>283892</v>
+      </c>
+      <c r="D12">
         <v>1078973096.78</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>0.03619588619759224</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.01887296540590055</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G12">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H12">
         <v>3.619588619759224</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>1.887296540590055</v>
       </c>
     </row>
@@ -2242,23 +2280,26 @@
         </is>
       </c>
       <c r="C13">
+        <v>306275</v>
+      </c>
+      <c r="D13">
         <v>990146048.22</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>0.02290605900133662</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.01731923823736954</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G13">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H13">
         <v>2.290605900133662</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>1.731923823736954</v>
       </c>
     </row>
@@ -2274,23 +2315,26 @@
         </is>
       </c>
       <c r="C14">
+        <v>675598</v>
+      </c>
+      <c r="D14">
         <v>2562583888.81</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>0.07049848664210395</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0.04482369136687609</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G14">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H14">
         <v>7.049848664210395</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>4.482369136687609</v>
       </c>
     </row>
@@ -2306,23 +2350,26 @@
         </is>
       </c>
       <c r="C15">
+        <v>372134</v>
+      </c>
+      <c r="D15">
         <v>1202924802.61</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>0.03440060917127755</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0.02104107901606681</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G15">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H15">
         <v>3.440060917127755</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>2.104107901606681</v>
       </c>
     </row>
@@ -2338,23 +2385,26 @@
         </is>
       </c>
       <c r="C16">
+        <v>468522</v>
+      </c>
+      <c r="D16">
         <v>2120033849.32</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>0.03138103348631988</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>0.03708278326583037</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G16">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H16">
         <v>3.138103348631987</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>3.708278326583037</v>
       </c>
     </row>
@@ -2370,23 +2420,26 @@
         </is>
       </c>
       <c r="C17">
+        <v>423536</v>
+      </c>
+      <c r="D17">
         <v>6837566518.55</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>0.01774539803593836</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>0.1195999758939773</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>1.774539803593836</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>11.95999758939773</v>
       </c>
     </row>
@@ -2402,23 +2455,26 @@
         </is>
       </c>
       <c r="C18">
+        <v>501306</v>
+      </c>
+      <c r="D18">
         <v>2039768606.41</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>0.04982071041328871</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0.03567881577372384</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G18">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H18">
         <v>4.98207104132887</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>3.567881577372384</v>
       </c>
     </row>
@@ -2434,23 +2490,26 @@
         </is>
       </c>
       <c r="C19">
+        <v>453527</v>
+      </c>
+      <c r="D19">
         <v>1956937590.38</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>0.05776210461891745</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>0.03422996880549536</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G19">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H19">
         <v>5.776210461891745</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>3.422996880549536</v>
       </c>
     </row>
@@ -2466,23 +2525,26 @@
         </is>
       </c>
       <c r="C20">
+        <v>163083</v>
+      </c>
+      <c r="D20">
         <v>918890507.58</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>0.021319194803451</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.01607286485003414</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G20">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H20">
         <v>2.1319194803451</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>1.607286485003414</v>
       </c>
     </row>
@@ -2498,23 +2560,26 @@
         </is>
       </c>
       <c r="C21">
+        <v>187216</v>
+      </c>
+      <c r="D21">
         <v>1335237845.73</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>0.02476472440077774</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.02335544579036864</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G21">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H21">
         <v>2.476472440077774</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>2.335544579036864</v>
       </c>
     </row>
@@ -2530,23 +2595,26 @@
         </is>
       </c>
       <c r="C22">
+        <v>337654</v>
+      </c>
+      <c r="D22">
         <v>1939351672.66</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>0.007949529934269608</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.0339223629738476</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>0.7949529934269608</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>3.39223629738476</v>
       </c>
     </row>
@@ -2562,23 +2630,26 @@
         </is>
       </c>
       <c r="C23">
+        <v>243728</v>
+      </c>
+      <c r="D23">
         <v>776448481.35</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>0.01470567515443555</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.01358132595864943</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G23">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H23">
         <v>1.470567515443555</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>1.358132595864943</v>
       </c>
     </row>
@@ -2594,23 +2665,26 @@
         </is>
       </c>
       <c r="C24">
+        <v>285815</v>
+      </c>
+      <c r="D24">
         <v>997429393.05</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>0.006306371387863901</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>0.01744663558900514</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>0.6306371387863901</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>1.744663558900514</v>
       </c>
     </row>
@@ -2626,23 +2700,26 @@
         </is>
       </c>
       <c r="C25">
+        <v>165138</v>
+      </c>
+      <c r="D25">
         <v>1294481417.88</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>0.04188065349285796</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>0.0226425506726158</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G25">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H25">
         <v>4.188065349285796</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>2.26425506726158</v>
       </c>
     </row>
@@ -2658,23 +2735,26 @@
         </is>
       </c>
       <c r="C26">
+        <v>480218</v>
+      </c>
+      <c r="D26">
         <v>1785675753.86</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>0.03550998362496413</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>0.03123432533149316</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G26">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H26">
         <v>3.550998362496413</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>3.123432533149316</v>
       </c>
     </row>
@@ -2690,23 +2770,26 @@
         </is>
       </c>
       <c r="C27">
+        <v>380513</v>
+      </c>
+      <c r="D27">
         <v>2301085241.03</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>0.04493881006046815</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>0.04024966171964013</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G27">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H27">
         <v>4.493881006046815</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>4.024966171964013</v>
       </c>
     </row>
@@ -2722,23 +2805,26 @@
         </is>
       </c>
       <c r="C28">
+        <v>469766</v>
+      </c>
+      <c r="D28">
         <v>1705356170.99</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>0.03328667005479251</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>0.02982940734656313</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G28">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H28">
         <v>3.328667005479251</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>2.982940734656313</v>
       </c>
     </row>
@@ -2754,23 +2840,26 @@
         </is>
       </c>
       <c r="C29">
+        <v>266497</v>
+      </c>
+      <c r="D29">
         <v>989484961.0599999</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>0.01278087722546964</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>0.01730767476545518</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G29">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H29">
         <v>1.278087722546964</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>1.730767476545518</v>
       </c>
     </row>
@@ -2786,23 +2875,26 @@
         </is>
       </c>
       <c r="C30">
+        <v>318913</v>
+      </c>
+      <c r="D30">
         <v>1376552981.17</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>0.01442360309469943</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>0.0240781135975885</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>1.442360309469943</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>2.40781135975885</v>
       </c>
     </row>
@@ -2818,23 +2910,26 @@
         </is>
       </c>
       <c r="C31">
+        <v>276069</v>
+      </c>
+      <c r="D31">
         <v>1594437761.49</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>0.01471389456597418</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>0.02788926693748503</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>1.471389456597418</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>2.788926693748503</v>
       </c>
     </row>
@@ -2850,23 +2945,26 @@
         </is>
       </c>
       <c r="C32">
+        <v>203874</v>
+      </c>
+      <c r="D32">
         <v>1144062973.34</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>0.01564514619986043</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>0.02001149146577848</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G32">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H32">
         <v>1.564514619986043</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>2.001149146577848</v>
       </c>
     </row>
@@ -2882,23 +2980,26 @@
         </is>
       </c>
       <c r="C33">
+        <v>605383</v>
+      </c>
+      <c r="D33">
         <v>3217471932.62</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>0.08227494643576272</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>0.05627873082286368</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="G33">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="H33">
         <v>8.227494643576271</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>5.627873082286368</v>
       </c>
     </row>
